--- a/data/company.xlsx
+++ b/data/company.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F54573-35DC-4DE4-9133-98693A7BD915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805B3081-A4B0-49B2-B358-09DCE99C618A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F431666B-F42A-443C-958A-45C32C2A9576}"/>
+    <workbookView xWindow="32640" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{F431666B-F42A-443C-958A-45C32C2A9576}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5067" uniqueCount="3946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5069" uniqueCount="3948">
   <si>
     <t>울산광역시 남구 중앙로166번길 51</t>
   </si>
@@ -11983,6 +11983,14 @@
   </si>
   <si>
     <t>www.ulleung.go.kr</t>
+  </si>
+  <si>
+    <t>담당자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이메일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -12409,7 +12417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8808F76B-FB14-4599-BE83-C8B95F3DD1BB}">
-  <dimension ref="A1:E1015"/>
+  <dimension ref="A1:G1015"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
@@ -12419,7 +12427,7 @@
     <col min="5" max="5" width="65.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>1195</v>
       </c>
@@ -12435,8 +12443,14 @@
       <c r="E1" s="2" t="s">
         <v>3793</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="3" t="s">
+        <v>3946</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12453,7 +12467,7 @@
         <v>3828</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12470,7 +12484,7 @@
         <v>3829</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12487,7 +12501,7 @@
         <v>3830</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12504,7 +12518,7 @@
         <v>3831</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12521,7 +12535,7 @@
         <v>3832</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12538,7 +12552,7 @@
         <v>3833</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12555,7 +12569,7 @@
         <v>3834</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12572,7 +12586,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12589,7 +12603,7 @@
         <v>3836</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12606,7 +12620,7 @@
         <v>3837</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12623,7 +12637,7 @@
         <v>3838</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12640,7 +12654,7 @@
         <v>3839</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12657,7 +12671,7 @@
         <v>3840</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
         <v>3794</v>
       </c>
@@ -12674,7 +12688,7 @@
         <v>3841</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
         <v>3794</v>
       </c>
